--- a/data/nzd0035/nzd0035.xlsx
+++ b/data/nzd0035/nzd0035.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F547"/>
+  <dimension ref="A1:F554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13558,6 +13558,174 @@
         <v>389.71</v>
       </c>
       <c r="F547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>358.64</v>
+      </c>
+      <c r="C548" t="n">
+        <v>374.71</v>
+      </c>
+      <c r="D548" t="n">
+        <v>374.92</v>
+      </c>
+      <c r="E548" t="n">
+        <v>389.71</v>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>357.75</v>
+      </c>
+      <c r="C549" t="n">
+        <v>374.77</v>
+      </c>
+      <c r="D549" t="n">
+        <v>375.83</v>
+      </c>
+      <c r="E549" t="n">
+        <v>390.8</v>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>357.13</v>
+      </c>
+      <c r="C550" t="n">
+        <v>375.36</v>
+      </c>
+      <c r="D550" t="n">
+        <v>375.6</v>
+      </c>
+      <c r="E550" t="n">
+        <v>391.79</v>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>357.26</v>
+      </c>
+      <c r="C551" t="n">
+        <v>375.77</v>
+      </c>
+      <c r="D551" t="n">
+        <v>375.7</v>
+      </c>
+      <c r="E551" t="n">
+        <v>393.34</v>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>356.79</v>
+      </c>
+      <c r="C552" t="n">
+        <v>375.89</v>
+      </c>
+      <c r="D552" t="n">
+        <v>376.11</v>
+      </c>
+      <c r="E552" t="n">
+        <v>394.67</v>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>356.65</v>
+      </c>
+      <c r="C553" t="n">
+        <v>376.59</v>
+      </c>
+      <c r="D553" t="n">
+        <v>376.67</v>
+      </c>
+      <c r="E553" t="n">
+        <v>395.41</v>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>356.75</v>
+      </c>
+      <c r="C554" t="n">
+        <v>376.97</v>
+      </c>
+      <c r="D554" t="n">
+        <v>377.19</v>
+      </c>
+      <c r="E554" t="n">
+        <v>393.95</v>
+      </c>
+      <c r="F554" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13574,7 +13742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B609"/>
+  <dimension ref="A1:B616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19667,6 +19835,76 @@
       </c>
       <c r="B609" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>-0.57</v>
       </c>
     </row>
   </sheetData>
@@ -19835,28 +20073,28 @@
         <v>0.0611</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02549737861811585</v>
+        <v>0.01486686822218424</v>
       </c>
       <c r="J2" t="n">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="K2" t="n">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00229574583669212</v>
+        <v>0.0007900147057917639</v>
       </c>
       <c r="M2" t="n">
-        <v>3.337622771034862</v>
+        <v>3.351395693632395</v>
       </c>
       <c r="N2" t="n">
-        <v>17.31478762110507</v>
+        <v>17.36410849166373</v>
       </c>
       <c r="O2" t="n">
-        <v>4.161104134854723</v>
+        <v>4.167026336809467</v>
       </c>
       <c r="P2" t="n">
-        <v>361.2405526931046</v>
+        <v>361.3492935932302</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19913,28 +20151,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05675804286316099</v>
+        <v>0.04977160805188275</v>
       </c>
       <c r="J3" t="n">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="K3" t="n">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009265218486312676</v>
+        <v>0.007285083302967288</v>
       </c>
       <c r="M3" t="n">
-        <v>3.72197915596848</v>
+        <v>3.710224683942315</v>
       </c>
       <c r="N3" t="n">
-        <v>21.33970013842667</v>
+        <v>21.19339209423747</v>
       </c>
       <c r="O3" t="n">
-        <v>4.619491328969746</v>
+        <v>4.603628144652592</v>
       </c>
       <c r="P3" t="n">
-        <v>377.2779189208537</v>
+        <v>377.348731530957</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19991,28 +20229,28 @@
         <v>0.0502</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03155579851765277</v>
+        <v>0.01999401476642714</v>
       </c>
       <c r="J4" t="n">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="K4" t="n">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002367063052111651</v>
+        <v>0.0009646623787439301</v>
       </c>
       <c r="M4" t="n">
-        <v>4.047254220376304</v>
+        <v>4.056824005915811</v>
       </c>
       <c r="N4" t="n">
-        <v>25.99866485610795</v>
+        <v>25.99277385175889</v>
       </c>
       <c r="O4" t="n">
-        <v>5.098888590281999</v>
+        <v>5.098310882219609</v>
       </c>
       <c r="P4" t="n">
-        <v>380.2580227279751</v>
+        <v>380.3752286419855</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20069,28 +20307,28 @@
         <v>0.0301</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1852534608452913</v>
+        <v>0.1767431869338231</v>
       </c>
       <c r="J5" t="n">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="K5" t="n">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03322670528640326</v>
+        <v>0.03100446325547823</v>
       </c>
       <c r="M5" t="n">
-        <v>5.930234512330358</v>
+        <v>5.908525761585904</v>
       </c>
       <c r="N5" t="n">
-        <v>61.85883981351245</v>
+        <v>61.29570229391938</v>
       </c>
       <c r="O5" t="n">
-        <v>7.865039085313718</v>
+        <v>7.829157189245812</v>
       </c>
       <c r="P5" t="n">
-        <v>391.5755968137075</v>
+        <v>391.6618298652381</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20128,7 +20366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F547"/>
+  <dimension ref="A1:F554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37627,6 +37865,230 @@
         </is>
       </c>
     </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>-34.950514385197096,173.6197644546269</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>-34.95121936498288,173.6198447515775</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>-34.951864943953545,173.62015755355526</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>-34.952316089822155,173.6208432564286</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>-34.95051355942776,173.6197547593646</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>-34.951219289930805,173.61984540233092</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>-34.95186071444522,173.62016609383804</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>-34.95230968941169,173.62085231598255</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>-34.95051298417227,173.6197480053618</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>-34.95121855191841,173.619851801406</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>-34.951861783441885,173.6201639353051</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>-34.95230387619428,173.6208605443835</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>-34.95051310479039,173.61974942152366</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>-34.951218039062134,173.61985624822086</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>-34.95186131866072,173.62016487379768</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>-34.95229477469115,173.62087342723117</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>-34.95051266870942,173.61974430155382</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>-34.951217888957835,173.61985754972764</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>-34.95185941305792,173.62016872161718</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>-34.9522869650132,173.62088448154336</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>-34.950512538812916,173.61974277645643</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>-34.95121701334913,173.61986514185037</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>-34.95185681028315,173.62017397717517</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-34.95228261977841,173.62089063206201</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>-34.95051263159613,173.6197438658117</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>-34.951216538018485,173.61986926328834</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>-34.95185439342065,173.6201788573359</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>-34.9522911928089,173.6208784972543</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0035/nzd0035.xlsx
+++ b/data/nzd0035/nzd0035.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F554"/>
+  <dimension ref="A1:F559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13726,6 +13726,126 @@
         <v>393.95</v>
       </c>
       <c r="F554" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>356.75</v>
+      </c>
+      <c r="C555" t="n">
+        <v>377.72</v>
+      </c>
+      <c r="D555" t="n">
+        <v>377.94</v>
+      </c>
+      <c r="E555" t="n">
+        <v>392.86</v>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>356.74</v>
+      </c>
+      <c r="C556" t="n">
+        <v>378.23</v>
+      </c>
+      <c r="D556" t="n">
+        <v>378.62</v>
+      </c>
+      <c r="E556" t="n">
+        <v>393.53</v>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>356.87</v>
+      </c>
+      <c r="C557" t="n">
+        <v>378.75</v>
+      </c>
+      <c r="D557" t="n">
+        <v>379.26</v>
+      </c>
+      <c r="E557" t="n">
+        <v>394.06</v>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>357.3</v>
+      </c>
+      <c r="C558" t="n">
+        <v>379.7</v>
+      </c>
+      <c r="D558" t="n">
+        <v>380.15</v>
+      </c>
+      <c r="E558" t="n">
+        <v>394.69</v>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>357.99</v>
+      </c>
+      <c r="C559" t="n">
+        <v>380.09</v>
+      </c>
+      <c r="D559" t="n">
+        <v>380.21</v>
+      </c>
+      <c r="E559" t="n">
+        <v>394.08</v>
+      </c>
+      <c r="F559" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13742,7 +13862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B616"/>
+  <dimension ref="A1:B621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19905,6 +20025,56 @@
       </c>
       <c r="B616" t="n">
         <v>-0.57</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -20073,28 +20243,28 @@
         <v>0.0611</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01486686822218424</v>
+        <v>0.007472183740785138</v>
       </c>
       <c r="J2" t="n">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="K2" t="n">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007900147057917639</v>
+        <v>0.0002011414732886463</v>
       </c>
       <c r="M2" t="n">
-        <v>3.351395693632395</v>
+        <v>3.360574735586753</v>
       </c>
       <c r="N2" t="n">
-        <v>17.36410849166373</v>
+        <v>17.39687262695652</v>
       </c>
       <c r="O2" t="n">
-        <v>4.167026336809467</v>
+        <v>4.170955840926217</v>
       </c>
       <c r="P2" t="n">
-        <v>361.3492935932302</v>
+        <v>361.4251910813323</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20151,28 +20321,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04977160805188275</v>
+        <v>0.05009873006766787</v>
       </c>
       <c r="J3" t="n">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="K3" t="n">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007285083302967288</v>
+        <v>0.007511669403815868</v>
       </c>
       <c r="M3" t="n">
-        <v>3.710224683942315</v>
+        <v>3.684107809706421</v>
       </c>
       <c r="N3" t="n">
-        <v>21.19339209423747</v>
+        <v>21.01086171758654</v>
       </c>
       <c r="O3" t="n">
-        <v>4.603628144652592</v>
+        <v>4.583760652301399</v>
       </c>
       <c r="P3" t="n">
-        <v>377.348731530957</v>
+        <v>377.3453845301246</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20229,28 +20399,28 @@
         <v>0.0502</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01999401476642714</v>
+        <v>0.01733652212432749</v>
       </c>
       <c r="J4" t="n">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="K4" t="n">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0009646623787439301</v>
+        <v>0.0007377884342921748</v>
       </c>
       <c r="M4" t="n">
-        <v>4.056824005915811</v>
+        <v>4.034388954845551</v>
       </c>
       <c r="N4" t="n">
-        <v>25.99277385175889</v>
+        <v>25.79128998661913</v>
       </c>
       <c r="O4" t="n">
-        <v>5.098310882219609</v>
+        <v>5.078512576199761</v>
       </c>
       <c r="P4" t="n">
-        <v>380.3752286419855</v>
+        <v>380.4022553102447</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20307,28 +20477,28 @@
         <v>0.0301</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1767431869338231</v>
+        <v>0.1726256714652017</v>
       </c>
       <c r="J5" t="n">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="K5" t="n">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03100446325547823</v>
+        <v>0.03011394750853535</v>
       </c>
       <c r="M5" t="n">
-        <v>5.908525761585904</v>
+        <v>5.881665467760977</v>
       </c>
       <c r="N5" t="n">
-        <v>61.29570229391938</v>
+        <v>60.80863762084633</v>
       </c>
       <c r="O5" t="n">
-        <v>7.829157189245812</v>
+        <v>7.797989331926938</v>
       </c>
       <c r="P5" t="n">
-        <v>391.6618298652381</v>
+        <v>391.7037215513186</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20366,7 +20536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F554"/>
+  <dimension ref="A1:F559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38089,6 +38259,166 @@
         </is>
       </c>
     </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>-34.95051263159613,173.6197438658117</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>-34.95121559986549,173.61987739770527</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>-34.95185090756096,173.62018589602872</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>-34.952297593221296,173.62086943770447</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>-34.95051262231781,173.61974375687618</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>-34.95121496192114,173.61988292910866</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>-34.95184774704782,173.62019227777637</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>-34.952293659022935,173.62087500641874</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>-34.950512742935985,173.61974517303804</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>-34.95121431146782,173.61988856897085</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>-34.951844772446904,173.62019828412667</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>-34.95229054689569,173.62087941152072</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>-34.95051314190366,173.6197498572658</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>-34.95121312313897,173.61989887256502</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>-34.95184063589204,173.6202066367068</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>-34.952286847574406,173.6208846477736</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>-34.95051378210722,173.61975737381735</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>-34.95121263529844,173.61990310246148</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>-34.951840357023144,173.62020719980205</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>-34.952290429456916,173.620879577751</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0035/nzd0035.xlsx
+++ b/data/nzd0035/nzd0035.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F559"/>
+  <dimension ref="A1:F562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13846,6 +13846,78 @@
         <v>394.08</v>
       </c>
       <c r="F559" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>357.85</v>
+      </c>
+      <c r="C560" t="n">
+        <v>380.44</v>
+      </c>
+      <c r="D560" t="n">
+        <v>380.06</v>
+      </c>
+      <c r="E560" t="n">
+        <v>395.37</v>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:17+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>358.24</v>
+      </c>
+      <c r="C561" t="n">
+        <v>380.4</v>
+      </c>
+      <c r="D561" t="n">
+        <v>380.06</v>
+      </c>
+      <c r="E561" t="n">
+        <v>395.37</v>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>357.49</v>
+      </c>
+      <c r="C562" t="n">
+        <v>380.84</v>
+      </c>
+      <c r="D562" t="n">
+        <v>380.37</v>
+      </c>
+      <c r="E562" t="n">
+        <v>394.21</v>
+      </c>
+      <c r="F562" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13862,7 +13934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B621"/>
+  <dimension ref="A1:B624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20075,6 +20147,36 @@
       </c>
       <c r="B621" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -20243,28 +20345,28 @@
         <v>0.0611</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007472183740785138</v>
+        <v>0.003879515646078976</v>
       </c>
       <c r="J2" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K2" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002011414732886463</v>
+        <v>5.457894940030794e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.360574735586753</v>
+        <v>3.361782143542801</v>
       </c>
       <c r="N2" t="n">
-        <v>17.39687262695652</v>
+        <v>17.3789361005759</v>
       </c>
       <c r="O2" t="n">
-        <v>4.170955840926217</v>
+        <v>4.168805116646244</v>
       </c>
       <c r="P2" t="n">
-        <v>361.4251910813323</v>
+        <v>361.4622582620307</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20321,28 +20423,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05009873006766787</v>
+        <v>0.0518541819750315</v>
       </c>
       <c r="J3" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K3" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007511669403815868</v>
+        <v>0.008122161304198294</v>
       </c>
       <c r="M3" t="n">
-        <v>3.684107809706421</v>
+        <v>3.675001328371348</v>
       </c>
       <c r="N3" t="n">
-        <v>21.01086171758654</v>
+        <v>20.91686014629929</v>
       </c>
       <c r="O3" t="n">
-        <v>4.583760652301399</v>
+        <v>4.573495396991155</v>
       </c>
       <c r="P3" t="n">
-        <v>377.3453845301246</v>
+        <v>377.3274267484322</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20399,28 +20501,28 @@
         <v>0.0502</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01733652212432749</v>
+        <v>0.01666597018596359</v>
       </c>
       <c r="J4" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K4" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007377884342921748</v>
+        <v>0.0006891485960095478</v>
       </c>
       <c r="M4" t="n">
-        <v>4.034388954845551</v>
+        <v>4.016271405208029</v>
       </c>
       <c r="N4" t="n">
-        <v>25.79128998661913</v>
+        <v>25.65613722401052</v>
       </c>
       <c r="O4" t="n">
-        <v>5.078512576199761</v>
+        <v>5.065188764894209</v>
       </c>
       <c r="P4" t="n">
-        <v>380.4022553102447</v>
+        <v>380.4091123128869</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20477,28 +20579,28 @@
         <v>0.0301</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1726256714652017</v>
+        <v>0.1712976059315967</v>
       </c>
       <c r="J5" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K5" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03011394750853535</v>
+        <v>0.02997137829544505</v>
       </c>
       <c r="M5" t="n">
-        <v>5.881665467760977</v>
+        <v>5.858570150951484</v>
       </c>
       <c r="N5" t="n">
-        <v>60.80863762084633</v>
+        <v>60.49545687237896</v>
       </c>
       <c r="O5" t="n">
-        <v>7.797989331926938</v>
+        <v>7.777882544264792</v>
       </c>
       <c r="P5" t="n">
-        <v>391.7037215513186</v>
+        <v>391.7173120520395</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20536,7 +20638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F559"/>
+  <dimension ref="A1:F562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38419,6 +38521,102 @@
         </is>
       </c>
     </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>-34.95051365221088,173.61975584871993</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>-34.95121219749272,173.61990689852237</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>-34.95184105419536,173.6202057920639</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>-34.952282854655984,173.62089029960157</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:17+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>-34.95051401406492,173.61976009720564</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>-34.95121224752767,173.61990646468684</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>-34.95184105419536,173.6202057920639</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>-34.952282854655984,173.62089029960157</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>-34.95051331819164,173.61975192704085</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>-34.9512116971432,173.6199112368776</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>-34.95183961337276,173.62020870138937</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>-34.95228966610493,173.62088065824764</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
